--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/DISCO FREIO - 01_2.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/DISCO FREIO - 01_2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DISCO FREIO TRASEIRO BRAVIC XRE00/ NX400 FALCON BMA86011</t>
+          <t>DISCO FREIO TRASEIRO BRAVIC XRE/ NX400 FALCON BMA86011</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -579,7 +568,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +584,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -617,7 +604,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -638,7 +624,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -659,7 +644,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -680,7 +664,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -701,7 +684,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -714,17 +696,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DISCO FREIO TRASEIRO IRON NXR150-160/ XRE190 182621</t>
+          <t>DISCO FREIO TRASEIRO IRON BROS NXR150-160/ XRE190 182621</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
     </row>
@@ -747,11 +724,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -772,7 +744,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -793,11 +764,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -818,7 +784,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -839,7 +804,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -856,11 +820,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -879,11 +838,6 @@
       <c r="D22" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>110</t>
         </is>
       </c>
     </row>
